--- a/reports/二级子公司C_利润表_2026-05.xlsx
+++ b/reports/二级子公司C_利润表_2026-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>93518335</v>
+        <v>95715511</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>90813040</v>
+        <v>90908184</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>397604720</v>
+        <v>396764023</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>424360</v>
+        <v>424636</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1973480</v>
+        <v>1978455</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>371315</v>
+        <v>370627</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1726795</v>
+        <v>1730968</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>318270</v>
+        <v>316987</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1480110</v>
+        <v>1482902</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>297052</v>
+        <v>295418</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1381436</v>
+        <v>1382852</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>159135</v>
+        <v>158180</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>740055</v>
+        <v>740042</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>127308</v>
+        <v>126615</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>592044</v>
+        <v>591419</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>91820895</v>
+        <v>94023048</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>89115600</v>
+        <v>89215721</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84872000</v>
+        <v>84938497</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>369976000</v>
+        <v>369130950</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1273080</v>
+        <v>1277096</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>5920440</v>
+        <v>5907626</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>848720</v>
+        <v>852938</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3946960</v>
+        <v>3941312</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3182700</v>
+        <v>3201515</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>14801100</v>
+        <v>14794504</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>424360</v>
+        <v>426827</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1973480</v>
+        <v>1974700</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>318270</v>
+        <v>319763</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1480110</v>
+        <v>1482438</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>530450</v>
+        <v>531905</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2466850</v>
+        <v>2472402</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>636540</v>
+        <v>636739</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2960220</v>
+        <v>2967717</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2652250</v>
+        <v>2646490</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>12334250</v>
+        <v>12363472</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>53045</v>
+        <v>51280</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>246685</v>
+        <v>258004</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1265918</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5925728</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>843639</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3946331</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>63388775</v>
+        <v>67867061</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>56439880</v>
+        <v>56364097</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>55166800</v>
+        <v>55089595</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>256552400</v>
+        <v>255920199</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1273080</v>
+        <v>1274502</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>5920440</v>
+        <v>5905669</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2129091</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>9846812</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>682474</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3153428</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>426889</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1972879</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>512145</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2369964</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>383632</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1779120</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>255237</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1186827</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>212175</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>989244</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>954810</v>
+        <v>952439</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4440330</v>
+        <v>4450607</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>742630</v>
+        <v>739285</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3453590</v>
+        <v>3459408</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>636540</v>
+        <v>632890</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2960220</v>
+        <v>2962465</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4774050</v>
+        <v>4745625</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>22201650</v>
+        <v>22194960</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>212180</v>
+        <v>211092</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>986740</v>
+        <v>985449</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>371315</v>
+        <v>359275</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1726795</v>
+        <v>1799130</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>424360</v>
+        <v>359275</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1973480</v>
+        <v>1799130</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>53045</v>
+        <v>51574</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>246685</v>
+        <v>256862</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>186087</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>925019</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>373289</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1724746</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>124340</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>617721</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>93220</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>463775</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>155155</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>773687</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>531578</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2472691</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82370</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>413026</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61628</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>309722</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>102514</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>515912</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>71680</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>360822</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51196</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>257462</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40996</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>205763</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30804</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>154198</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28432120</v>
+        <v>27452188</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33259215</v>
+        <v>30946035</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>213022</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>984855</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51781</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>257165</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>84872</v>
+        <v>82894</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>394696</v>
+        <v>411870</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28347248</v>
+        <v>27582316</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2970520</v>
+        <v>2895523</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>13814360</v>
+        <v>14443708</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25376728</v>
+        <v>24686793</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25376728</v>
+        <v>24686793</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25376728</v>
+        <v>24686793</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25376728</v>
+        <v>24686793</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25376728</v>
+        <v>24686793</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
